--- a/data/trans_dic/P1402-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1402-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 1,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,85</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,35</t>
+          <t>0,0; 1,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -757,12 +757,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,22</t>
+          <t>0,2; 1,23</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,36</t>
+          <t>0,43; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,64</t>
+          <t>0,26; 3,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,35</t>
+          <t>0,14; 1,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,74</t>
+          <t>0,65; 2,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,97</t>
+          <t>0,32; 1,79</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,95</t>
+          <t>0,08; 0,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,14</t>
+          <t>0,75; 2,11</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,19</t>
+          <t>0,28; 1,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,02</t>
+          <t>0,2; 1,95</t>
         </is>
       </c>
     </row>
@@ -944,19 +944,19 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1,84%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,14%</t>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,11</t>
+          <t>1,49; 4,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,15; 1,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,32</t>
+          <t>0,99; 3,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,31</t>
+          <t>1,2; 3,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,12</t>
+          <t>0,44; 1,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 3,02</t>
+          <t>0,99; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,18</t>
+          <t>0,48; 2,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,12</t>
+          <t>1,05; 2,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,61</t>
+          <t>1,11; 2,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,93</t>
+          <t>0,72; 1,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,33</t>
+          <t>1,0; 2,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,3</t>
+          <t>1,35; 2,86</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,46</t>
+          <t>2,76; 6,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,16</t>
+          <t>2,82; 6,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,73</t>
+          <t>3,73; 7,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 7,83</t>
+          <t>5,34; 9,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,12</t>
+          <t>2,52; 5,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,31</t>
+          <t>2,07; 5,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,17</t>
+          <t>2,22; 5,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,39</t>
+          <t>2,23; 4,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,77</t>
+          <t>3,06; 5,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,17</t>
+          <t>2,86; 5,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,85</t>
+          <t>3,39; 5,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,39</t>
+          <t>4,05; 6,43</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,01</t>
+          <t>8,66; 14,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 15,14</t>
+          <t>8,96; 15,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,33; 16,76</t>
+          <t>10,43; 16,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,34; 15,67</t>
+          <t>10,29; 15,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,91</t>
+          <t>9,43; 15,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,84; 14,56</t>
+          <t>8,55; 15,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 15,73</t>
+          <t>9,98; 15,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 9,71</t>
+          <t>6,27; 9,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,84; 14,48</t>
+          <t>9,66; 14,27</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 14,02</t>
+          <t>9,51; 13,81</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,62; 15,14</t>
+          <t>10,63; 15,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,05</t>
+          <t>8,93; 11,85</t>
         </is>
       </c>
     </row>
@@ -1364,27 +1364,27 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>22,13%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
           <t>22,91%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,29%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>15,13; 24,26</t>
+          <t>15,36; 23,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>25,6; 36,58</t>
+          <t>24,5; 36,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23,6; 33,26</t>
+          <t>23,6; 33,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,34; 25,96</t>
+          <t>19,05; 26,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18,34; 26,76</t>
+          <t>18,6; 27,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,79; 30,05</t>
+          <t>20,67; 29,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,87; 27,32</t>
+          <t>18,35; 27,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,71; 17,71</t>
+          <t>14,56; 19,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,16; 24,28</t>
+          <t>18,29; 24,24</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,44; 31,38</t>
+          <t>24,26; 31,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,28; 29,27</t>
+          <t>22,19; 28,84</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,78; 20,31</t>
+          <t>17,53; 21,68</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,22; 25,39</t>
+          <t>15,03; 25,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>22,67; 34,74</t>
+          <t>22,86; 34,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29,28; 40,18</t>
+          <t>29,07; 40,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25,43; 33,9</t>
+          <t>25,78; 34,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>17,2; 26,52</t>
+          <t>17,2; 27,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,5; 36,32</t>
+          <t>26,61; 36,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,61; 34,03</t>
+          <t>23,51; 33,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26,04; 32,06</t>
+          <t>25,74; 31,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17,8; 24,8</t>
+          <t>17,7; 25,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26,79; 34,17</t>
+          <t>26,41; 33,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27,49; 34,99</t>
+          <t>26,7; 34,36</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26,75; 31,91</t>
+          <t>26,75; 31,95</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,43</t>
+          <t>4,98; 6,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,61; 8,43</t>
+          <t>6,61; 8,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,8</t>
+          <t>7,86; 9,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,84</t>
+          <t>8,37; 10,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,95; 7,66</t>
+          <t>5,96; 7,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 9,62</t>
+          <t>7,71; 9,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 9,53</t>
+          <t>7,4; 9,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,04</t>
+          <t>7,12; 8,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5,71; 6,85</t>
+          <t>5,68; 6,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,76</t>
+          <t>7,47; 8,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7,91; 9,31</t>
+          <t>7,91; 9,22</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,82; 8,68</t>
+          <t>7,93; 9,05</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1105</t>
         </is>
       </c>
     </row>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4869</t>
+          <t>0; 5357</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>899; 8410</t>
+          <t>894; 8263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5660</t>
+          <t>0; 4700</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 8696</t>
+          <t>0; 7216</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2103,27 +2103,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5468</t>
+          <t>0; 6332</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4907</t>
+          <t>0; 5870</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1875; 10782</t>
+          <t>1807; 10854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4677</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 7182</t>
+          <t>0; 5738</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5781</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>803</t>
+          <t>776</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6574</t>
+          <t>6557</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 10411</t>
+          <t>0; 8917</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2959; 16221</t>
+          <t>2948; 15944</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 8357</t>
+          <t>0; 8495</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1351; 15413</t>
+          <t>1227; 16054</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>886; 8429</t>
+          <t>883; 9132</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3964; 16745</t>
+          <t>3973; 17871</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1794; 11103</t>
+          <t>1792; 10091</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 4655</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1780; 12906</t>
+          <t>1152; 13412</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9649; 27708</t>
+          <t>9784; 27388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3227; 13688</t>
+          <t>3256; 14869</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1931; 18928</t>
+          <t>1909; 19057</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9850</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>11095</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16532</t>
+          <t>24856</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9066; 26247</t>
+          <t>9501; 26219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>931; 9589</t>
+          <t>1024; 9844</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6700; 22219</t>
+          <t>6626; 22324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4893; 17733</t>
+          <t>7461; 22741</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3053; 14654</t>
+          <t>3012; 13442</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7153; 21419</t>
+          <t>7035; 21683</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3649; 14396</t>
+          <t>3196; 13708</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3490; 11479</t>
+          <t>6522; 17718</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14029; 34675</t>
+          <t>14765; 35440</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10863; 26915</t>
+          <t>10006; 26338</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12742; 31045</t>
+          <t>13244; 30993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9978; 24778</t>
+          <t>16823; 35549</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>48822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>23245</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66043</t>
+          <t>72067</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14981; 33558</t>
+          <t>14338; 33776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18197; 37872</t>
+          <t>17340; 37548</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25001; 49955</t>
+          <t>24094; 48834</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19211; 69547</t>
+          <t>37420; 66727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13894; 31558</t>
+          <t>13007; 30504</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12945; 32639</t>
+          <t>12708; 32277</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14456; 33545</t>
+          <t>14440; 33858</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>15441; 31312</t>
+          <t>16408; 31375</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>31899; 59685</t>
+          <t>31651; 57772</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>35337; 63487</t>
+          <t>35125; 63500</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>43631; 75740</t>
+          <t>43882; 76751</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>40039; 86215</t>
+          <t>58220; 92458</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72299</t>
+          <t>78425</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>42767</t>
+          <t>47868</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>115065</t>
+          <t>126293</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>32652; 58043</t>
+          <t>33485; 57089</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37955; 65022</t>
+          <t>38484; 66939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>49372; 80081</t>
+          <t>49850; 80958</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57915; 87810</t>
+          <t>62581; 94349</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37787; 64283</t>
+          <t>38094; 63632</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39574; 65215</t>
+          <t>38292; 67192</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47744; 78159</t>
+          <t>49574; 79124</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>35218; 52884</t>
+          <t>38092; 58057</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>77837; 114492</t>
+          <t>76349; 112869</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82171; 123001</t>
+          <t>83422; 121143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103568; 147586</t>
+          <t>103633; 148189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>99496; 133169</t>
+          <t>108627; 144098</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83684</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>74695</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>151584</t>
+          <t>164018</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>44258; 70972</t>
+          <t>44938; 70141</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79302; 113325</t>
+          <t>75900; 113446</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>78904; 111187</t>
+          <t>78897; 112179</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70647; 94806</t>
+          <t>76894; 105031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>62882; 91766</t>
+          <t>63791; 92840</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>73609; 106374</t>
+          <t>73170; 105480</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71275; 103197</t>
+          <t>69318; 103648</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>28659; 107739</t>
+          <t>63927; 86258</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>115393; 154285</t>
+          <t>116226; 154018</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>162248; 208326</t>
+          <t>161047; 209540</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>158682; 208458</t>
+          <t>158000; 205343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>75780; 197723</t>
+          <t>147731; 182695</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84042</t>
+          <t>92048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>122762</t>
+          <t>133030</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>206804</t>
+          <t>225078</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>31945; 53283</t>
+          <t>31550; 54210</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>56636; 86798</t>
+          <t>57117; 85959</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75257; 103273</t>
+          <t>74721; 102829</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>71905; 95843</t>
+          <t>79959; 107013</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>57438; 88565</t>
+          <t>57428; 90481</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>103090; 141260</t>
+          <t>103502; 142697</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94497; 136160</t>
+          <t>94093; 135192</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>110478; 136025</t>
+          <t>119140; 147281</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>96801; 134873</t>
+          <t>96256; 136200</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>171166; 218318</t>
+          <t>168683; 214500</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>180663; 229956</t>
+          <t>175469; 225827</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>189119; 225624</t>
+          <t>206772; 247005</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>299869</t>
+          <t>328160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>263819</t>
+          <t>291814</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>563688</t>
+          <t>619974</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>161041; 210802</t>
+          <t>163060; 212361</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>226653; 288927</t>
+          <t>226560; 292023</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>268492; 332542</t>
+          <t>266855; 331080</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235490; 339621</t>
+          <t>295171; 360639</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>201167; 258756</t>
+          <t>201539; 255318</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>274080; 342156</t>
+          <t>273925; 343177</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>263158; 337702</t>
+          <t>262473; 336372</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>210216; 294073</t>
+          <t>265737; 316192</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>380100; 455760</t>
+          <t>377762; 457589</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>518037; 611320</t>
+          <t>521469; 609828</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>548885; 646291</t>
+          <t>548676; 639499</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>484867; 617312</t>
+          <t>575425; 656432</t>
         </is>
       </c>
     </row>
